--- a/tests/data/testTopology_C+L_PATH_expected.xlsx
+++ b/tests/data/testTopology_C+L_PATH_expected.xlsx
@@ -388,6 +388,9 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.0 ms
 	- Actual pch out:: 0.00 dBm
+	- CD penalty: None dB
+	- PMD penalty:: None dB
+	- PDL penalty:: None dB
 </t>
         </is>
       </c>
@@ -537,6 +540,9 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.61 ms
 	- Actual pch out:: 0.00 dBm
+	- CD penalty: None dB
+	- PMD penalty:: None dB
+	- PDL penalty:: None dB
 </t>
         </is>
       </c>

--- a/tests/data/testTopology_C+L_PATH_expected.xlsx
+++ b/tests/data/testTopology_C+L_PATH_expected.xlsx
@@ -388,9 +388,6 @@
 	- PDL:: 0.00 dB
 	- Latency: 0.0 ms
 	- Actual pch out:: 0.00 dBm
-	- CD penalty: None dB
-	- PMD penalty:: None dB
-	- PDL penalty:: None dB
 </t>
         </is>
       </c>
